--- a/evaluation/results/Qualitative Evaluations - System 1, System 2 and System 3/LLMs4Subjects-Evaluation-Sheet-mat.xlsx
+++ b/evaluation/results/Qualitative Evaluations - System 1, System 2 and System 3/LLMs4Subjects-Evaluation-Sheet-mat.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SadruddinS\Data\GermEval25\Qualitative Evaluations\Evaluation with LA2I2F\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DSouzaJ\Datasets\subject-indexing-dataset\evaluation\results\Qualitative Evaluations - System 1, System 2 and System 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543C074A-A40A-4530-A03E-54D1475957FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19170" windowHeight="5910"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LLMs4Subjects Evaluation Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1104,25 +1110,25 @@
     <t>Ordnungstheorie | gnd:4172736-8</t>
   </si>
   <si>
-    <t>LA2I2F - Team 1</t>
-  </si>
-  <si>
     <t>Code</t>
   </si>
   <si>
-    <t>DNB-AI - Team 2</t>
-  </si>
-  <si>
-    <t>Annif - Team 3</t>
-  </si>
-  <si>
     <t xml:space="preserve">I </t>
+  </si>
+  <si>
+    <t>System 1</t>
+  </si>
+  <si>
+    <t>System 2</t>
+  </si>
+  <si>
+    <t>System 3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1204,9 +1210,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1244,9 +1250,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1281,7 +1287,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1316,7 +1322,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1489,7 +1495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K201"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1523,22 +1529,22 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -3785,7 +3791,7 @@
         <v>282</v>
       </c>
       <c r="G76" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="J76" t="s">
         <v>104</v>
